--- a/part definitions.xlsx
+++ b/part definitions.xlsx
@@ -145,11 +145,11 @@
   <tableColumns count="13">
     <tableColumn id="1" name="Part"/>
     <tableColumn id="2" name="Category"/>
-    <tableColumn id="3" name="tip holder 1000"/>
-    <tableColumn id="4" name="tip holder 100"/>
+    <tableColumn id="3" name="Tip Holder 1000"/>
+    <tableColumn id="4" name="Tip Holder 100"/>
     <tableColumn id="5" name="MO:HEAT"/>
-    <tableColumn id="6" name="tube holder 8T2"/>
-    <tableColumn id="7" name="tube holder 888"/>
+    <tableColumn id="6" name="Tube Holder 8T2"/>
+    <tableColumn id="7" name="Tube Holder 888"/>
     <tableColumn id="8" name="MO:TILT PASSIVE"/>
     <tableColumn id="9" name="MO:TILT"/>
     <tableColumn id="10" name="MO:COOL 2ml"/>
@@ -481,12 +481,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>tip holder 1000</t>
+          <t>Tip Holder 1000</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tip holder 100</t>
+          <t>Tip Holder 100</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -496,12 +496,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tube holder 8T2</t>
+          <t>Tube Holder 8T2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>tube holder 888</t>
+          <t>Tube Holder 888</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -538,12 +538,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bottom plate</t>
+          <t>Bottom Plate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cnc metal</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -583,12 +583,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>top plate</t>
+          <t>Top Plate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cnc metal</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -610,12 +610,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cooling tubes block</t>
+          <t>Cooling Tubes Block</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cnc metal</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -635,12 +635,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>50 ml holder</t>
+          <t>50 ml Holder</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cnc metal</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
@@ -660,12 +660,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8 ml holder</t>
+          <t>8 ml Holder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cnc metal</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -687,12 +687,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trash</t>
+          <t>Trash</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mechanical part</t>
+          <t>MECH</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -759,12 +759,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spring plungers 6 mm</t>
+          <t>Spring Plungers 6 mm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mechanical part</t>
+          <t>MECH</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -804,12 +804,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spring plungers 5 mm</t>
+          <t>Spring Plungers 5 mm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mechanical part</t>
+          <t>MECH</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -829,12 +829,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Thermal Mat adhesive</t>
+          <t>Thermal Mat Adhesive</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mechanical part</t>
+          <t>MECH</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mechanical part</t>
+          <t>MECH</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -884,7 +884,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mechanical part</t>
+          <t>MECH</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
@@ -904,12 +904,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mill-max connector</t>
+          <t>Mill-Max Connector</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -941,12 +941,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>temperature sensor</t>
+          <t>Temperature Sensor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -968,12 +968,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>heating mat</t>
+          <t>Heating Mat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -993,12 +993,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fan big</t>
+          <t>Fan Big</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
@@ -1018,12 +1018,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fan small</t>
+          <t>Fan Small</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1093,12 +1093,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Voltage step down</t>
+          <t>Voltage Step Down</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>electronics</t>
+          <t>ELECT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frog passive</t>
+          <t>Frog Passive</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pcb</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1151,12 +1151,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frog active</t>
+          <t>Frog Active</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pcb</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>heater body</t>
+          <t>Heater Body</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -1211,12 +1211,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tilting body</t>
+          <t>Tilting Body</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
@@ -1236,12 +1236,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tip holder bottom</t>
+          <t>Tip Holder Bottom</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1263,12 +1263,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tip holder top 1000</t>
+          <t>Tip Holder Top 1000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1288,12 +1288,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tip holder top 100</t>
+          <t>Tip Holder Top 100</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
@@ -1313,12 +1313,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tube holder bottom</t>
+          <t>Tube Holder Bottom</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
@@ -1340,12 +1340,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tube holder top</t>
+          <t>Tube Holder Top</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -1367,12 +1367,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tube holder Trash</t>
+          <t>Tube Holder Trash</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
@@ -1394,12 +1394,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cooler bottom</t>
+          <t>Cooler Bottom</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -1419,12 +1419,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cooler top</t>
+          <t>Cooler Top</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
@@ -1444,12 +1444,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cooler screw cover</t>
+          <t>Cooler Screw Cover</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -1469,12 +1469,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>frog holder</t>
+          <t>Frog Holder</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1514,12 +1514,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>magnet stopper</t>
+          <t>Magnet Stopper</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3d printing</t>
+          <t>3DPRT</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1559,7 +1559,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid category" error="Choose a category from the list" type="list">
-      <formula1>"mechanical part,electronics,3d printing,cnc metal,pcb"</formula1>
+      <formula1>"MECH,ELECT,3DPRT,CNC,PCB"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/part definitions.xlsx
+++ b/part definitions.xlsx
@@ -1559,7 +1559,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid category" error="Choose a category from the list" type="list">
-      <formula1>"MECH,ELECT,3DPRT,CNC,PCB"</formula1>
+      <formula1>"CNC,MECH,ELECT,PCB,3DPRT"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
